--- a/src/test/resources/data.xlsx
+++ b/src/test/resources/data.xlsx
@@ -13,7 +13,7 @@
   <calcPr calcId="0"/>
   <oleSize ref="A1:M5"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="11">
   <si>
     <t>samson</t>
   </si>
@@ -51,12 +51,16 @@
   </si>
   <si>
     <t>d</t>
+  </si>
+  <si>
+    <t>sam</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -420,12 +424,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F792C232-8C48-49DA-8686-6A11D2C361A8}">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="13.28515625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="24.28515625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="20.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -455,7 +459,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>

--- a/src/test/resources/data.xlsx
+++ b/src/test/resources/data.xlsx
@@ -3,17 +3,18 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{E1DF2558-160C-4298-A975-99AB82E97832}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{2F6AB4E1-8966-4072-9051-CEF6140C81B3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15870" windowHeight="4905" xr2:uid="{8666860D-7FE1-4D9B-88DC-AC3EA951CFC0}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15990" windowHeight="3570" activeTab="1" xr2:uid="{8666860D-7FE1-4D9B-88DC-AC3EA951CFC0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:M5"/>
+  <oleSize ref="A1:P13"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t>samson</t>
   </si>
@@ -47,20 +48,34 @@
     <t>value</t>
   </si>
   <si>
-    <t>TASTY</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
     <t>sam</t>
+  </si>
+  <si>
+    <t>nothing</t>
+  </si>
+  <si>
+    <t>vaibhav</t>
+  </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>ppr</t>
+  </si>
+  <si>
+    <t>sunny</t>
+  </si>
+  <si>
+    <t>javed</t>
+  </si>
+  <si>
+    <t>praveen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -424,12 +439,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F792C232-8C48-49DA-8686-6A11D2C361A8}">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="13.28515625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="24.28515625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="20.140625"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -459,249 +474,61 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="1"/>
-    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>9</v>
-      </c>
-    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{D4986BD0-BE86-4D31-9126-CE8B0A3EFDB6}"/>
@@ -710,4 +537,119 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{864A5434-0938-4F61-892B-17AAAB31E80D}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{329FCCA5-76AB-4BEB-BA99-6ECB87A654C6}"/>
+    <hyperlink ref="B4" r:id="rId2" xr:uid="{C47E8196-D200-49D6-A5A1-AC1754005FBE}"/>
+    <hyperlink ref="B6" r:id="rId3" xr:uid="{4D5F64F2-912F-4310-9A7D-4B78863686EB}"/>
+    <hyperlink ref="B8" r:id="rId4" xr:uid="{6C241C34-566A-4824-A534-FCBF3D17581D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/resources/data.xlsx
+++ b/src/test/resources/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{2F6AB4E1-8966-4072-9051-CEF6140C81B3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{910612D8-24B6-432F-AD6B-BC5D54CF6F15}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15990" windowHeight="3570" activeTab="1" xr2:uid="{8666860D-7FE1-4D9B-88DC-AC3EA951CFC0}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15990" windowHeight="1695" activeTab="1" xr2:uid="{8666860D-7FE1-4D9B-88DC-AC3EA951CFC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
   <si>
     <t>samson</t>
   </si>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t>praveen</t>
+  </si>
+  <si>
+    <t>dsd</t>
   </si>
 </sst>
 </file>
@@ -571,7 +574,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>

--- a/src/test/resources/data.xlsx
+++ b/src/test/resources/data.xlsx
@@ -3,16 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{910612D8-24B6-432F-AD6B-BC5D54CF6F15}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{F8F63C94-48F4-4427-8493-404C81954B51}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15990" windowHeight="1695" activeTab="1" xr2:uid="{8666860D-7FE1-4D9B-88DC-AC3EA951CFC0}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16440" windowHeight="3300" activeTab="1" xr2:uid="{8666860D-7FE1-4D9B-88DC-AC3EA951CFC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:P13"/>
+  <oleSize ref="A1:P9"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
   <si>
     <t>samson</t>
   </si>
@@ -57,12 +57,6 @@
     <t>vaibhav</t>
   </si>
   <si>
-    <t>abc</t>
-  </si>
-  <si>
-    <t>ppr</t>
-  </si>
-  <si>
     <t>sunny</t>
   </si>
   <si>
@@ -72,7 +66,31 @@
     <t>praveen</t>
   </si>
   <si>
-    <t>dsd</t>
+    <t>dsd.SUM@GMAIL</t>
+  </si>
+  <si>
+    <t>ddd.SUM@GMAIL</t>
+  </si>
+  <si>
+    <t>cdfsf</t>
+  </si>
+  <si>
+    <t>fdgfg</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>hd</t>
+  </si>
+  <si>
+    <t>fg</t>
+  </si>
+  <si>
+    <t>jgfj</t>
+  </si>
+  <si>
+    <t>jfj</t>
   </si>
 </sst>
 </file>
@@ -546,6 +564,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{864A5434-0938-4F61-892B-17AAAB31E80D}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -573,11 +596,11 @@
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
         <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -588,62 +611,62 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
-        <v>11</v>
+      <c r="B5" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="B9" t="s">
-        <v>11</v>
+      <c r="B9" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -652,6 +675,10 @@
     <hyperlink ref="B4" r:id="rId2" xr:uid="{C47E8196-D200-49D6-A5A1-AC1754005FBE}"/>
     <hyperlink ref="B6" r:id="rId3" xr:uid="{4D5F64F2-912F-4310-9A7D-4B78863686EB}"/>
     <hyperlink ref="B8" r:id="rId4" xr:uid="{6C241C34-566A-4824-A534-FCBF3D17581D}"/>
+    <hyperlink ref="B3" r:id="rId5" xr:uid="{991A4237-EDA7-47C0-8A98-267CFEA3D9FB}"/>
+    <hyperlink ref="B5" r:id="rId6" xr:uid="{E98A4722-3C27-424C-ADC6-A57D99817141}"/>
+    <hyperlink ref="B7" r:id="rId7" xr:uid="{0EB1BAD2-5D65-4E52-9796-B769DBAB2B95}"/>
+    <hyperlink ref="B9" r:id="rId8" xr:uid="{2C820C99-B73E-49F6-89A0-84FC750A6486}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
